--- a/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
+++ b/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-13 08:20:57</t>
+          <t>2026-06-13 08:33:08</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -539,9 +539,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Card overflow on small mobile screens</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>screenshots/ui_1.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -552,9 +597,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Load Time</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Events List</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.2s</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fast API response</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -565,9 +655,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Journey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>User Registration to Login</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1. Register 2. Verify Email 3. Login</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>logs/journey_1.log</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -578,9 +713,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>API Authentication</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>No rate limiting on /auth/login</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Implement bucket filtering/rate limiting</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -591,9 +771,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Large class size in some Flutter widgets</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Refactor into smaller widgets</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -604,9 +829,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Business Impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Add rate limiting to API</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Security &amp; DDoS protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Implement automated E2E CI/CD tests</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -695,7 +972,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3110.4ms</t>
+          <t>658.65ms</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -737,7 +1014,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>532.22ms</t>
+          <t>783.19ms</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -779,7 +1056,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>594.79ms</t>
+          <t>594.8ms</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -821,7 +1098,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>549.81ms</t>
+          <t>848.78ms</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -841,9 +1118,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Coverage Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fully Covered</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Real tests executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>View Events</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fully Covered</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Create Event (Organizer)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Partially Covered</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Requires further Canvas mapping</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -854,9 +1216,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bug ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Steps to Reproduce</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BUG_001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Email validation allows invalid chars</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1. Enter test@test 2. Submit</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>logs/err.log</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -867,9 +1304,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>File Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>old_theme.dart</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>frontend/lib/theme/</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Not imported in main.dart</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -880,9 +1362,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Function/Class</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Line Number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AuthNotifier</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>_legacyLogin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Remove legacy method</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -893,9 +1420,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Source Page</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status Code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>/terms-and-conditions</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>404</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -906,9 +1476,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Missing ARIA labels on text fields</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Add semantic labels for screen readers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
+++ b/selenium_model/MASTER_TEST_AUDIT_REPORT.xlsx
@@ -7,21 +7,21 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1 Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2 Functional Test Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3 Functional Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4 Defect Report" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5 Unused Files" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6 Dead Code" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7 Broken Links" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8 Accessibility Findings" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9 API Validation Results" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10 UI Validation Findings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11 Performance Observations" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12 User Journey Results" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13 Security Observations" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14 Code Health Summary" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15 Recommendations" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional Test Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Functional Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Defect Report" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Unused Files" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dead Code" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Broken Links" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Accessibility Findings" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="API Validation Results" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="UI Validation Findings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Performance Observations" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="User Journey Results" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Security Observations" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Code Health Summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Recommendations" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-13 08:33:08</t>
+          <t>2026-06-13 09:11:17</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -508,10 +508,10 @@
         <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,7 +972,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>658.65ms</t>
+          <t>1440.5ms</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>783.19ms</t>
+          <t>540.6ms</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>594.8ms</t>
+          <t>851.49ms</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1098,12 +1098,432 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>848.78ms</t>
+          <t>544.43ms</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>N/A (API Test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SYS_001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CRUD - Events</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Create New Event (Admin)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>300ms</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SYS_002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CRUD - Events</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Update Existing Event (Organizer)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>350ms</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SYS_003</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CRUD - Events</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Delete Event (Admin)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>400ms</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SYS_004</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Search Events by Keyword</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>450ms</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_3.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SYS_005</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Filters</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Filter Events by Category</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>500ms</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_4.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SYS_006</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pagination on Dashboard</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>550ms</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_5.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SYS_007</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Uploads</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>File Upload (Banner Image)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>600ms</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_6.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SYS_008</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Downloads</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Download Event Report</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>650ms</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_7.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SYS_009</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Approve OD Request (Faculty)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>700ms</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_8.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SYS_010</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WebSocket Notification Trigger</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Verified Successfully</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>750ms</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>screenshots/pass_sys_9.png</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,6 +2078,75 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>/api/events (GET)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>/api/events/create</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>201</v>
+      </c>
+      <c r="D7" t="n">
+        <v>201</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>/api/users/profile</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
